--- a/assets/dcf/Cluck & Pluck.xlsx
+++ b/assets/dcf/Cluck & Pluck.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox\Courses\Teaching\Financial Analytics\Course\6 - Discounted Cash Flow &amp; Real Options\4 - Exercises\2 - Case\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9421E270-C334-41F4-8664-96A1A9160BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9B6D0D-BD71-4B86-B130-881EECC3EFC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10876" firstSheet="1" activeTab="1" xr2:uid="{6394BC74-EAE9-47A1-8528-22ED1E30B107}"/>
   </bookViews>
@@ -318,12 +318,6 @@
     <t>After the first year, you will gain a better understanding about the growth prospects of the business.</t>
   </si>
   <si>
-    <t>For years 2 through 5, the sales growth rate is assumed to be Normally distributed with mean 0% and standard deviation 3%. It assumed there is a singleshort-run growth for the restaurant (i.e. the growth rate for year 2 will be the same as the growth rates for years 3, 4 and 5).</t>
-  </si>
-  <si>
-    <t>After year 5, you assume the free cash flows will continue to grow indefintely at the same growth rate as the short-run sales growth rate.</t>
-  </si>
-  <si>
     <t>DCF Analysis</t>
   </si>
   <si>
@@ -333,31 +327,37 @@
     <t>Real Option Analysis</t>
   </si>
   <si>
-    <t>If things go well, you will expand your operations and add 20 aditional restuarants.</t>
-  </si>
-  <si>
-    <t>At the end of year 5, you will assess how well your resturant business is performing.</t>
-  </si>
-  <si>
     <t>Terminal Value of Expansion</t>
   </si>
   <si>
-    <t>If you decide to expand, you will need to invest an additional $2,000 in working capital and $3,000 in new resturant buildings. These investments will be made in year 5.</t>
-  </si>
-  <si>
-    <t>The new restuarants will begin producing cash flows starting in year 6. To keep the analysis tractable, it is assumed the free cash flow of each new resturant will be the same as the free cash flow of the original resturant. For example, the FCF in year 6 of the expansion will equal the FCF in year 6 of the original resturant times 20.</t>
-  </si>
-  <si>
     <t>You will only invest in the expansion if it has a positive NPV.</t>
   </si>
   <si>
-    <t>Find the NPV of the resturant business that includes the option to expand if the business is performing well.</t>
-  </si>
-  <si>
     <t>Find the probability the NPV will be positive.</t>
   </si>
   <si>
     <t>Using Crystal Ball, plot the distribution of the NPV.</t>
+  </si>
+  <si>
+    <t>For years 2 through 5, the sales growth rate is assumed to be Normally distributed with mean 0% and standard deviation 3%. It assumed there is a single short-run growth for the restaurant (i.e. the growth rate for year 2 will be the same as the growth rates for years 3, 4 and 5).</t>
+  </si>
+  <si>
+    <t>After year 5, you assume the free cash flows will continue to grow indefinitely at the same growth rate as the short-run sales growth rate.</t>
+  </si>
+  <si>
+    <t>At the end of year 5, you will assess how well your restaurant business is performing.</t>
+  </si>
+  <si>
+    <t>If things go well, you will expand your operations and add 20 additional restaurants.</t>
+  </si>
+  <si>
+    <t>If you decide to expand, you will need to invest an additional $2,000 in working capital and $3,000 in new restaurant buildings. These investments will be made in year 5.</t>
+  </si>
+  <si>
+    <t>The new restaurants will begin producing cash flows starting in year 6. To keep the analysis tractable, it is assumed the free cash flow of each new restaurant will be the same as the free cash flow of the original restaurant. For example, the FCF in year 6 of the expansion will equal the FCF in year 6 of the original restaurant times 20.</t>
+  </si>
+  <si>
+    <t>Find the NPV of the restaurant business that includes the option to expand if the business is performing well.</t>
   </si>
 </sst>
 </file>
@@ -1153,7 +1153,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.45">
@@ -1208,7 +1208,7 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A19" s="11" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.45">
@@ -1218,57 +1218,57 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A23" s="11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A27" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1783,7 +1783,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B36" s="47"/>
       <c r="C36" s="47"/>
